--- a/темы для совпадений.xlsx
+++ b/темы для совпадений.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonProject2\Sovpadenie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155AFDDD-4DCE-43E4-B90B-E717E895B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847C15F-E9E6-432F-90C2-F0E3D2B9007C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3735" yWindow="3630" windowWidth="15870" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -453,9 +453,6 @@
     <t>owl</t>
   </si>
   <si>
-    <t>larks</t>
-  </si>
-  <si>
     <t>blitz</t>
   </si>
   <si>
@@ -490,6 +487,9 @@
   </si>
   <si>
     <t>Класc в Днд</t>
+  </si>
+  <si>
+    <t>lark</t>
   </si>
 </sst>
 </file>
@@ -779,13 +779,13 @@
         <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
         <v>1</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D80" t="s">
         <v>1</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
         <v>1</v>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95" t="s">
         <v>1</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D97" t="s">
         <v>1</v>
@@ -1609,7 +1609,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D98" t="s">
         <v>1</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D100" t="s">
         <v>1</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D105" t="s">
         <v>1</v>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D125" t="s">
         <v>1</v>
